--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -17325,12 +17325,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -17364,81 +17364,95 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17465,17 +17479,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17500,7 +17514,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -17509,81 +17523,170 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17748,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -17790,7 +17893,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -17905,12 +18008,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17935,12 +18038,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -17983,40 +18086,330 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW115" t="inlineStr">
+      <c r="AW117" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY115" t="inlineStr">
+      <c r="AY117" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
+      <c r="AZ117" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA115" t="inlineStr">
+      <c r="BA117" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB115" t="inlineStr">
+      <c r="BB117" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC115" t="inlineStr">
+      <c r="BC117" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -18138,7 +18531,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -18148,7 +18541,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -18168,7 +18561,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -18200,7 +18593,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -18298,12 +18298,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -18328,12 +18328,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -18376,40 +18376,185 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW117" t="inlineStr">
+      <c r="AW118" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
+      <c r="AX118" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY117" t="inlineStr">
+      <c r="AY118" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
+      <c r="AZ118" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA117" t="inlineStr">
+      <c r="BA118" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB117" t="inlineStr">
+      <c r="BB118" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC117" t="inlineStr">
+      <c r="BC118" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -18531,7 +18676,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -18541,7 +18686,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -18593,7 +18738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -18560,6 +18560,151 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18593,7 +18738,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -18676,7 +18821,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -18686,7 +18831,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -17325,12 +17325,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17364,95 +17364,81 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17465,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17528,98 +17514,23 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
+      <c r="R112" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Papegojsjuka</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -17713,17 +17624,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17748,7 +17659,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -17757,81 +17668,170 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -18443,12 +18443,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -18473,12 +18473,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -18521,42 +18521,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18588,12 +18588,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -18666,40 +18666,330 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AW120" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AX120" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr">
+      <c r="AY120" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
+      <c r="AZ120" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA119" t="inlineStr">
+      <c r="BA120" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB119" t="inlineStr">
+      <c r="BB120" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC119" t="inlineStr">
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18738,7 +19028,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18821,7 +19111,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -18831,7 +19121,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -18883,7 +19173,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -18627,13 +18627,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -18990,6 +18990,151 @@
         </is>
       </c>
       <c r="BC121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -19028,7 +19173,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -19111,7 +19256,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -19121,7 +19266,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -19173,7 +19318,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1492,6 +1517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1637,6 +1667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2072,6 +2117,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2613,6 +2663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2909,6 +2964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3205,6 +3265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3501,6 +3566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3797,6 +3867,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3945,6 +4020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4090,6 +4170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4235,6 +4320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4380,6 +4470,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4516,6 +4611,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4661,6 +4761,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4806,6 +4911,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4942,6 +5052,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5087,6 +5202,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5232,6 +5352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5921,6 +6046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6217,6 +6347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6513,6 +6648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6809,6 +6949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6957,6 +7102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7102,6 +7252,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7238,6 +7393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7383,6 +7543,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7528,6 +7693,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7673,6 +7843,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7818,6 +7993,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7963,6 +8143,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8108,6 +8293,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8253,6 +8443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8942,6 +9137,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9238,6 +9438,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9534,6 +9739,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9830,6 +10040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9975,6 +10190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10120,6 +10340,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10256,6 +10481,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10401,6 +10631,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10546,6 +10781,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10691,6 +10931,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10836,6 +11081,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10981,6 +11231,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11126,6 +11381,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11271,6 +11531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11960,6 +12225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12256,6 +12526,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12552,6 +12827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12848,6 +13128,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12993,6 +13278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13138,6 +13428,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13283,6 +13578,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13428,6 +13728,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13564,6 +13869,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13709,6 +14019,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13854,6 +14169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13999,6 +14319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14144,6 +14469,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14289,6 +14619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14978,6 +15313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15274,6 +15614,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15570,6 +15915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15866,6 +16216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16162,6 +16517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16307,6 +16667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16452,6 +16817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16588,6 +16958,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16733,6 +17108,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16878,6 +17258,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17023,6 +17408,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17168,6 +17558,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17304,6 +17699,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17449,6 +17849,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17594,6 +17999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18277,6 +18687,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18567,6 +18982,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18857,6 +19277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19147,6 +19572,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19292,6 +19722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19437,6 +19872,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19573,6 +20013,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19718,6 +20163,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19863,6 +20313,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20008,6 +20463,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20153,6 +20613,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20289,6 +20754,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20434,6 +20904,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20579,6 +21054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21262,6 +21742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21552,6 +22037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21842,6 +22332,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22132,6 +22627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22422,6 +22922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22567,6 +23072,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22703,6 +23213,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22839,6 +23354,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22984,6 +23504,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23129,6 +23654,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23274,6 +23804,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23419,6 +23954,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23564,6 +24104,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23709,6 +24254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24972,6 +25522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25117,6 +25672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25262,6 +25822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25407,6 +25972,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25552,6 +26122,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25697,6 +26272,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25842,6 +26422,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25978,6 +26563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26123,6 +26713,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26216,12 +26811,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -26246,7 +26841,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -26255,81 +26850,95 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26356,17 +26965,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -26391,7 +27000,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -26400,81 +27009,170 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Papegojsjuka</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM psittacosis category.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PSITTACOSIS</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26536,7 +27234,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -26681,7 +27379,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -26763,6 +27461,296 @@
         </is>
       </c>
       <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -26884,7 +27872,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -26894,7 +27882,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -26914,7 +27902,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -26946,7 +27934,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -25509,13 +25509,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R163" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -27751,6 +27751,151 @@
         </is>
       </c>
       <c r="BC177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27789,7 +27934,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -27872,7 +28017,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -27882,7 +28027,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -27934,7 +28079,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d112/2026-2029.xlsx
+++ b/diseases/d112/2026-2029.xlsx
@@ -12816,9 +12816,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -27898,6 +27895,156 @@
       <c r="BC178" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>psittacosis</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27934,7 +28081,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -28017,7 +28164,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -28027,7 +28174,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -28079,7 +28226,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
